--- a/data/processed/positivacao/2022-10_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2022-10_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -25153,7 +25153,7 @@
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B955" t="inlineStr"/>
@@ -36583,7 +36583,7 @@
     <row r="1395">
       <c r="A1395" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1395" t="inlineStr"/>
@@ -65657,7 +65657,7 @@
     <row r="2514">
       <c r="A2514" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2514" t="inlineStr"/>
@@ -67328,12 +67328,12 @@
       <c r="A2579" t="inlineStr"/>
       <c r="B2579" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 11 cliente(s), não positivou 87 cliente(s) - Total vendido: R$ 20.848,75
+          <t>Vendedor 1 - VENDEDOR 01: positivou 11 cliente(s), não positivou 87 cliente(s) - Total vendido: R$ 20.848,75
 Vendedor 18 - LOJA: positivou 108 cliente(s), não positivou 739 cliente(s) - Total vendido: R$ 96.586,73
-Vendedor 3 - FERNANDA: positivou 103 cliente(s), não positivou 336 cliente(s) - Total vendido: R$ 151.455,08
-Vendedor 4 - DANIELA: positivou 51 cliente(s), não positivou 609 cliente(s) - Total vendido: R$ 32.427,67
+Vendedor 3 - VENDEDOR 03: positivou 103 cliente(s), não positivou 336 cliente(s) - Total vendido: R$ 151.455,08
+Vendedor 4 - VENDEDOR 04: positivou 51 cliente(s), não positivou 609 cliente(s) - Total vendido: R$ 32.427,67
 Vendedor 5 - SITE: positivou 18 cliente(s), não positivou 439 cliente(s) - Total vendido: R$ 3.180,91
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2579" t="inlineStr"/>
